--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4528-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4528-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7989CF0-0192-4842-8757-7EAF53358B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A257100C-A7ED-4D66-B819-4548545F511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E237E833-A48F-42DB-B293-702956D1039A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F70D3E27-2EFF-4281-8ACB-4EDE2CC25AAD}"/>
   </bookViews>
   <sheets>
     <sheet name="4528-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1523,24 +1523,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165005BD-6570-4AC2-A4F6-DEE68D18BB21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358BB212-B04D-4AB2-9646-E2B123D33BEE}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1573,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1610,7 +1609,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1662,7 +1661,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1730,7 +1729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1874,7 +1873,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="42"/>
       <c r="C9" s="18" t="s">
@@ -2046,7 +2045,7 @@
       <c r="W9" s="48"/>
       <c r="X9" s="44"/>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2020</v>
       </c>
@@ -2118,7 +2117,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2019</v>
       </c>
@@ -2190,7 +2189,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2018</v>
       </c>
@@ -2262,7 +2261,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2017</v>
       </c>
@@ -2334,7 +2333,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2016</v>
       </c>
@@ -2406,7 +2405,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2015</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2014</v>
       </c>
@@ -2550,7 +2549,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2013</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2012</v>
       </c>
@@ -2694,7 +2693,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2011</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2010</v>
       </c>
@@ -2838,7 +2837,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2009</v>
       </c>
@@ -2910,7 +2909,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2008</v>
       </c>
@@ -2982,7 +2981,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2007</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2006</v>
       </c>
@@ -3126,7 +3125,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2005</v>
       </c>
@@ -3198,7 +3197,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2004</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2003</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2002</v>
       </c>
@@ -3414,7 +3413,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2001</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2000</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1999</v>
       </c>
@@ -3630,7 +3629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1998</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1997</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
         <v>55</v>
       </c>
